--- a/BEAST2/Data/Pterosaur ages_11-23 (version 2).xlsx
+++ b/BEAST2/Data/Pterosaur ages_11-23 (version 2).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\revbayes-v1.2.1-win64\revbayes-v1.2.1\Files\PterosaurPhylogeny\BEAST2\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3492C885-4F04-40F7-BFEA-D932F4B1B16B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C2CA393-4B8B-4A34-882D-A898430C51E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28905" yWindow="-11790" windowWidth="29040" windowHeight="17640" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28905" yWindow="-11790" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Defined ages" sheetId="1" r:id="rId1"/>
@@ -3278,7 +3278,7 @@
         <v>173.46499999999997</v>
       </c>
       <c r="F2">
-        <f>E2-146.17</f>
+        <f t="shared" ref="F2:F26" si="1">E2-146.17</f>
         <v>27.294999999999987</v>
       </c>
       <c r="G2">
@@ -3311,7 +3311,7 @@
         <v>213.5</v>
       </c>
       <c r="F3">
-        <f t="shared" ref="F3:F26" si="1">E3-146.17</f>
+        <f t="shared" si="1"/>
         <v>67.330000000000013</v>
       </c>
       <c r="G3">

--- a/BEAST2/Data/Pterosaur ages_11-23 (version 2).xlsx
+++ b/BEAST2/Data/Pterosaur ages_11-23 (version 2).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\revbayes-v1.2.1-win64\revbayes-v1.2.1\Files\PterosaurPhylogeny\BEAST2\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C2CA393-4B8B-4A34-882D-A898430C51E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CBDC586-6AA5-4DE7-95F8-B6AD7F694A0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28905" yWindow="-11790" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Defined ages" sheetId="1" r:id="rId1"/>
@@ -464,15 +464,6 @@
     <t>227.3-233.6</t>
   </si>
   <si>
-    <t>209.51-214.03</t>
-  </si>
-  <si>
-    <t>205.44-209.51</t>
-  </si>
-  <si>
-    <t>201.36-205.44</t>
-  </si>
-  <si>
     <t>239.48-241.46</t>
   </si>
   <si>
@@ -849,6 +840,15 @@
   </si>
   <si>
     <t>Carniadactylus_rosenfeldi-2</t>
+  </si>
+  <si>
+    <t>205.74-214.03</t>
+  </si>
+  <si>
+    <t>201.36-203.55</t>
+  </si>
+  <si>
+    <t>203.55-205.74</t>
   </si>
 </sst>
 </file>
@@ -894,7 +894,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="21">
+  <fills count="22">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1015,6 +1015,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -1043,7 +1049,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1081,6 +1087,7 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standaard" xfId="0" builtinId="0"/>
@@ -1376,7 +1383,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B1" t="s">
         <v>136</v>
@@ -1476,7 +1483,7 @@
         <v>227.3</v>
       </c>
       <c r="C8">
-        <v>209.51</v>
+        <v>205.74</v>
       </c>
       <c r="D8" t="s">
         <v>24</v>
@@ -1488,7 +1495,7 @@
       </c>
       <c r="B9">
         <f t="shared" si="0"/>
-        <v>209.51</v>
+        <v>205.74</v>
       </c>
       <c r="C9">
         <v>201.36</v>
@@ -1664,7 +1671,7 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B22">
         <v>259.55</v>
@@ -1675,12 +1682,12 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="21" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
@@ -1688,7 +1695,7 @@
         <v>84</v>
       </c>
       <c r="B27" s="21" t="s">
-        <v>140</v>
+        <v>266</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
@@ -1728,7 +1735,7 @@
         <v>111</v>
       </c>
       <c r="B34" s="21" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
@@ -1736,12 +1743,12 @@
         <v>112</v>
       </c>
       <c r="B35" s="21" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" s="22" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
@@ -1749,7 +1756,7 @@
         <v>85</v>
       </c>
       <c r="B39" s="22" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
@@ -1757,7 +1764,7 @@
         <v>81</v>
       </c>
       <c r="B40" s="22" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
@@ -1765,7 +1772,7 @@
         <v>86</v>
       </c>
       <c r="B41" s="22" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
@@ -1773,7 +1780,7 @@
         <v>131</v>
       </c>
       <c r="B43" s="22" t="s">
-        <v>142</v>
+        <v>267</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
@@ -1781,55 +1788,55 @@
         <v>132</v>
       </c>
       <c r="B44" s="22" t="s">
-        <v>141</v>
+        <v>268</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" s="22" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B46" s="22" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" s="22" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B47" s="22" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="22" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B49" s="22" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="22" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="B50" s="22" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="22" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B52" s="22" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="22" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B53" s="22" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
   </sheetData>
@@ -1875,7 +1882,7 @@
         <v>56</v>
       </c>
       <c r="G1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="H1" t="s">
         <v>59</v>
@@ -1924,7 +1931,7 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>28</v>
@@ -1948,7 +1955,7 @@
         <v>71</v>
       </c>
       <c r="I3" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="K3" s="13" t="s">
         <v>67</v>
@@ -1983,7 +1990,7 @@
         <v>78</v>
       </c>
       <c r="I4" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="K4" s="15" t="s">
         <v>69</v>
@@ -2064,16 +2071,16 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C7" s="29" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="D7" s="29" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="E7" s="15">
         <v>217.49</v>
@@ -2099,7 +2106,7 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>28</v>
@@ -2117,19 +2124,19 @@
         <v>199.46</v>
       </c>
       <c r="G8" s="27" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="H8" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="I8" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="K8" s="25" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="L8" s="25" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
@@ -2161,15 +2168,15 @@
         <v>97</v>
       </c>
       <c r="K9" s="16" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="L9" s="16" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>30</v>
@@ -2187,24 +2194,24 @@
         <v>224</v>
       </c>
       <c r="G10" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="H10" t="s">
         <v>119</v>
       </c>
       <c r="I10" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="K10" s="27" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="L10" s="27" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>30</v>
@@ -2222,10 +2229,10 @@
         <v>215</v>
       </c>
       <c r="G11" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="H11" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="I11" t="s">
         <v>118</v>
@@ -2235,7 +2242,7 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>28</v>
@@ -2253,13 +2260,13 @@
         <v>214.03</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H12" t="s">
         <v>102</v>
       </c>
       <c r="I12" s="16" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="K12" s="23"/>
       <c r="L12" s="23"/>
@@ -2439,13 +2446,13 @@
         <v>214.03</v>
       </c>
       <c r="G18" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="H18" t="s">
+        <v>252</v>
+      </c>
+      <c r="I18" s="16" t="s">
         <v>177</v>
-      </c>
-      <c r="H18" t="s">
-        <v>255</v>
-      </c>
-      <c r="I18" s="16" t="s">
-        <v>180</v>
       </c>
       <c r="K18" s="24"/>
       <c r="L18" s="24"/>
@@ -2457,17 +2464,17 @@
       <c r="B19" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C19" s="29" t="s">
+      <c r="C19" s="33" t="s">
         <v>84</v>
       </c>
-      <c r="D19" s="29" t="s">
+      <c r="D19" s="33" t="s">
         <v>84</v>
       </c>
       <c r="E19" s="14">
         <v>214.03</v>
       </c>
       <c r="F19" s="14">
-        <v>209.51</v>
+        <v>205.74</v>
       </c>
       <c r="G19" t="s">
         <v>92</v>
@@ -2476,7 +2483,7 @@
         <v>123</v>
       </c>
       <c r="I19" s="16" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="K19" s="23"/>
       <c r="L19" s="23"/>
@@ -2519,17 +2526,17 @@
       <c r="B21" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C21" s="29" t="s">
+      <c r="C21" s="33" t="s">
         <v>84</v>
       </c>
-      <c r="D21" s="29" t="s">
+      <c r="D21" s="33" t="s">
         <v>126</v>
       </c>
       <c r="E21" s="14">
         <v>214.03</v>
       </c>
       <c r="F21" s="13">
-        <v>205.44</v>
+        <v>203.55</v>
       </c>
       <c r="G21" t="s">
         <v>125</v>
@@ -2545,16 +2552,16 @@
     </row>
     <row r="22" spans="1:12" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="6" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>28</v>
       </c>
       <c r="C22" s="29" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="D22" s="29" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="E22" s="32">
         <v>152.01</v>
@@ -2563,13 +2570,13 @@
         <v>149.24</v>
       </c>
       <c r="G22" s="26" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="H22" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="I22" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="K22" s="23"/>
       <c r="L22" s="23"/>
@@ -2612,17 +2619,17 @@
       <c r="B24" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C24" s="29" t="s">
+      <c r="C24" s="33" t="s">
         <v>72</v>
       </c>
-      <c r="D24" s="29" t="s">
+      <c r="D24" s="33" t="s">
         <v>84</v>
       </c>
       <c r="E24" s="15">
         <v>217.49</v>
       </c>
       <c r="F24" s="14">
-        <v>209.51</v>
+        <v>205.74</v>
       </c>
       <c r="G24" t="s">
         <v>92</v>
@@ -2731,7 +2738,7 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>26</v>
@@ -2749,7 +2756,7 @@
         <v>56</v>
       </c>
       <c r="G1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="H1" t="s">
         <v>59</v>
@@ -2760,22 +2767,22 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="29" t="s">
+      <c r="C2" s="33" t="s">
         <v>84</v>
       </c>
-      <c r="D2" s="29" t="s">
+      <c r="D2" s="33" t="s">
         <v>84</v>
       </c>
       <c r="E2" s="14">
         <v>214.03</v>
       </c>
       <c r="F2" s="14">
-        <v>209.51</v>
+        <v>205.74</v>
       </c>
       <c r="G2" t="s">
         <v>92</v>
@@ -2784,36 +2791,36 @@
         <v>93</v>
       </c>
       <c r="I2" s="16" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="29" t="s">
-        <v>72</v>
-      </c>
-      <c r="D3" s="29" t="s">
-        <v>72</v>
+      <c r="C3" s="33" t="s">
+        <v>84</v>
+      </c>
+      <c r="D3" s="33" t="s">
+        <v>84</v>
       </c>
       <c r="E3" s="14">
         <v>214.03</v>
       </c>
       <c r="F3" s="14">
-        <v>209.51</v>
+        <v>205.74</v>
       </c>
       <c r="G3" s="16" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H3" t="s">
         <v>93</v>
       </c>
       <c r="I3" s="16" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="K3" s="17" t="s">
         <v>87</v>
@@ -2824,7 +2831,7 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>30</v>
@@ -2842,18 +2849,18 @@
         <v>215</v>
       </c>
       <c r="G4" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="H4" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="I4" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="30" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>30</v>
@@ -2871,18 +2878,18 @@
         <v>219.23</v>
       </c>
       <c r="G5" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="H5" t="s">
         <v>119</v>
       </c>
       <c r="I5" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>30</v>
@@ -2900,18 +2907,18 @@
         <v>205</v>
       </c>
       <c r="G6" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="H6" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="I6" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>30</v>
@@ -2929,27 +2936,27 @@
         <v>207</v>
       </c>
       <c r="G7" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="H7" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="I7" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="18" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>30</v>
       </c>
       <c r="C8" s="29" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D8" s="29" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E8" s="19">
         <f>F7</f>
@@ -2959,18 +2966,18 @@
         <v>202</v>
       </c>
       <c r="G8" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="H8" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="I8" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>28</v>
@@ -2979,7 +2986,7 @@
         <v>6</v>
       </c>
       <c r="D9" s="29" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="E9" s="17">
         <v>201.36</v>
@@ -2988,56 +2995,56 @@
         <v>196.18</v>
       </c>
       <c r="G9" s="26" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="H9" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="I9" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="29" t="s">
+      <c r="C10" s="33" t="s">
         <v>84</v>
       </c>
-      <c r="D10" s="29" t="s">
+      <c r="D10" s="33" t="s">
         <v>84</v>
       </c>
       <c r="E10" s="14">
         <v>214.03</v>
       </c>
       <c r="F10" s="14">
-        <v>209.51</v>
+        <v>205.74</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="H10" s="16" t="s">
+        <v>176</v>
+      </c>
+      <c r="I10" s="16" t="s">
         <v>179</v>
-      </c>
-      <c r="I10" s="16" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="6" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C11" s="29" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="D11" s="29" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="E11" s="13">
         <v>149.24</v>
@@ -3046,13 +3053,13 @@
         <v>146.16999999999999</v>
       </c>
       <c r="G11" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="H11" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="I11" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
   </sheetData>
@@ -3073,7 +3080,7 @@
   <sheetData>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B2" t="s">
         <v>1</v>
@@ -3082,10 +3089,10 @@
         <v>2</v>
       </c>
       <c r="E2" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F2" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -3099,7 +3106,7 @@
         <v>237</v>
       </c>
       <c r="D3" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="E3">
         <f t="shared" ref="E3:F7" si="0">B3-143.1</f>
@@ -3187,7 +3194,7 @@
         <v>143.1</v>
       </c>
       <c r="D7" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E7">
         <f t="shared" si="0"/>
@@ -3200,7 +3207,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B9">
         <v>259.55</v>
@@ -3209,7 +3216,7 @@
         <v>233.67</v>
       </c>
       <c r="D9" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="E9">
         <f>B9-146.17</f>
@@ -3254,10 +3261,10 @@
         <v>135</v>
       </c>
       <c r="G1" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="H1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
@@ -3290,7 +3297,7 @@
         <v>32.590000000000003</v>
       </c>
       <c r="I2" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -3323,7 +3330,7 @@
         <v>71.320000000000022</v>
       </c>
       <c r="I3" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
@@ -3356,7 +3363,7 @@
         <v>71.320000000000022</v>
       </c>
       <c r="I4" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
@@ -3389,7 +3396,7 @@
         <v>13.100000000000023</v>
       </c>
       <c r="I5" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
@@ -3422,7 +3429,7 @@
         <v>67.860000000000014</v>
       </c>
       <c r="I6" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
@@ -3455,7 +3462,7 @@
         <v>71.320000000000022</v>
       </c>
       <c r="I7" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
@@ -3488,7 +3495,7 @@
         <v>55.190000000000026</v>
       </c>
       <c r="I8" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
@@ -3521,7 +3528,7 @@
         <v>67.860000000000014</v>
       </c>
       <c r="I9" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
@@ -3554,7 +3561,7 @@
         <v>80.830000000000013</v>
       </c>
       <c r="I10" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
@@ -3587,7 +3594,7 @@
         <v>80.830000000000013</v>
       </c>
       <c r="I11" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
@@ -3620,7 +3627,7 @@
         <v>71.320000000000022</v>
       </c>
       <c r="I12" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
@@ -3653,7 +3660,7 @@
         <v>79.25</v>
       </c>
       <c r="I13" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
@@ -3686,7 +3693,7 @@
         <v>87.43</v>
       </c>
       <c r="I14" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
@@ -3719,7 +3726,7 @@
         <v>93.31</v>
       </c>
       <c r="I15" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
@@ -3752,7 +3759,7 @@
         <v>90.830000000000013</v>
       </c>
       <c r="I16" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
@@ -3785,7 +3792,7 @@
         <v>67.860000000000014</v>
       </c>
       <c r="I17" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
@@ -3818,7 +3825,7 @@
         <v>71.320000000000022</v>
       </c>
       <c r="I18" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
@@ -3832,26 +3839,26 @@
         <v>214.03</v>
       </c>
       <c r="D19" s="14">
-        <v>209.51</v>
+        <v>205.74</v>
       </c>
       <c r="E19">
         <f t="shared" si="0"/>
-        <v>211.76999999999998</v>
+        <v>209.88499999999999</v>
       </c>
       <c r="F19">
         <f t="shared" si="1"/>
-        <v>65.599999999999994</v>
+        <v>63.715000000000003</v>
       </c>
       <c r="G19">
         <f t="shared" si="2"/>
-        <v>63.34</v>
+        <v>59.570000000000022</v>
       </c>
       <c r="H19">
         <f t="shared" si="3"/>
         <v>67.860000000000014</v>
       </c>
       <c r="I19" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -3884,7 +3891,7 @@
         <v>85.230000000000018</v>
       </c>
       <c r="I20" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -3898,26 +3905,26 @@
         <v>214.03</v>
       </c>
       <c r="D21" s="13">
-        <v>205.44</v>
+        <v>203.55</v>
       </c>
       <c r="E21">
         <f t="shared" si="0"/>
-        <v>209.73500000000001</v>
+        <v>208.79000000000002</v>
       </c>
       <c r="F21">
         <f t="shared" si="1"/>
-        <v>63.565000000000026</v>
+        <v>62.620000000000033</v>
       </c>
       <c r="G21">
         <f t="shared" si="2"/>
-        <v>59.27000000000001</v>
+        <v>57.380000000000024</v>
       </c>
       <c r="H21">
         <f t="shared" si="3"/>
         <v>67.860000000000014</v>
       </c>
       <c r="I21" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -3950,7 +3957,7 @@
         <v>5.8400000000000034</v>
       </c>
       <c r="I22" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -3983,7 +3990,7 @@
         <v>87.43</v>
       </c>
       <c r="I23" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -3997,26 +4004,26 @@
         <v>217.49</v>
       </c>
       <c r="D24" s="14">
-        <v>209.51</v>
+        <v>205.74</v>
       </c>
       <c r="E24">
         <f t="shared" si="0"/>
-        <v>213.5</v>
+        <v>211.61500000000001</v>
       </c>
       <c r="F24">
         <f t="shared" si="1"/>
-        <v>67.330000000000013</v>
+        <v>65.445000000000022</v>
       </c>
       <c r="G24">
         <f t="shared" si="2"/>
-        <v>63.34</v>
+        <v>59.570000000000022</v>
       </c>
       <c r="H24">
         <f t="shared" si="3"/>
         <v>71.320000000000022</v>
       </c>
       <c r="I24" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -4049,7 +4056,7 @@
         <v>87.43</v>
       </c>
       <c r="I25" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -4082,7 +4089,7 @@
         <v>67.860000000000014</v>
       </c>
       <c r="I26" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
   </sheetData>
@@ -4122,15 +4129,15 @@
         <v>135</v>
       </c>
       <c r="G1" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="H1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>28</v>
@@ -4139,31 +4146,31 @@
         <v>214.03</v>
       </c>
       <c r="D2" s="14">
-        <v>209.51</v>
+        <v>205.74</v>
       </c>
       <c r="E2">
         <f t="shared" ref="E2:E4" si="0">(C2+D2)/2</f>
-        <v>211.76999999999998</v>
+        <v>209.88499999999999</v>
       </c>
       <c r="F2">
         <f t="shared" ref="F2:F4" si="1">E2-146.17</f>
-        <v>65.599999999999994</v>
+        <v>63.715000000000003</v>
       </c>
       <c r="G2">
         <f t="shared" ref="G2:G4" si="2">D2-146.17</f>
-        <v>63.34</v>
+        <v>59.570000000000022</v>
       </c>
       <c r="H2">
         <f t="shared" ref="H2:H4" si="3">C2-146.17</f>
         <v>67.860000000000014</v>
       </c>
       <c r="I2" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>28</v>
@@ -4172,31 +4179,31 @@
         <v>214.03</v>
       </c>
       <c r="D3" s="14">
-        <v>209.51</v>
+        <v>205.74</v>
       </c>
       <c r="E3">
         <f t="shared" si="0"/>
-        <v>211.76999999999998</v>
+        <v>209.88499999999999</v>
       </c>
       <c r="F3">
         <f t="shared" si="1"/>
-        <v>65.599999999999994</v>
+        <v>63.715000000000003</v>
       </c>
       <c r="G3">
         <f t="shared" si="2"/>
-        <v>63.34</v>
+        <v>59.570000000000022</v>
       </c>
       <c r="H3">
         <f t="shared" si="3"/>
         <v>67.860000000000014</v>
       </c>
       <c r="I3" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>30</v>
@@ -4224,12 +4231,12 @@
         <v>80.830000000000013</v>
       </c>
       <c r="I4" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="30" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>30</v>
@@ -4257,12 +4264,12 @@
         <v>73.380000000000024</v>
       </c>
       <c r="I5" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>30</v>
@@ -4290,12 +4297,12 @@
         <v>80.830000000000013</v>
       </c>
       <c r="I6" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>30</v>
@@ -4323,12 +4330,12 @@
         <v>68.830000000000013</v>
       </c>
       <c r="I7" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>30</v>
@@ -4357,12 +4364,12 @@
         <v>60.830000000000013</v>
       </c>
       <c r="I8" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>28</v>
@@ -4390,12 +4397,12 @@
         <v>55.190000000000026</v>
       </c>
       <c r="I9" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>28</v>
@@ -4404,31 +4411,31 @@
         <v>214.03</v>
       </c>
       <c r="D10" s="14">
-        <v>209.51</v>
+        <v>205.74</v>
       </c>
       <c r="E10">
         <f t="shared" si="8"/>
-        <v>211.76999999999998</v>
+        <v>209.88499999999999</v>
       </c>
       <c r="F10">
         <f t="shared" si="9"/>
-        <v>65.599999999999994</v>
+        <v>63.715000000000003</v>
       </c>
       <c r="G10">
         <f t="shared" si="10"/>
-        <v>63.34</v>
+        <v>59.570000000000022</v>
       </c>
       <c r="H10">
         <f t="shared" si="11"/>
         <v>67.860000000000014</v>
       </c>
       <c r="I10" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="6" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>28</v>
@@ -4456,7 +4463,7 @@
         <v>3.0700000000000216</v>
       </c>
       <c r="I11" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
   </sheetData>
@@ -4475,7 +4482,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B1">
         <v>26.615000000000009</v>
@@ -4483,7 +4490,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B2">
         <v>67.330000000000013</v>
@@ -4491,7 +4498,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B3">
         <v>65.599999999999994</v>
@@ -4499,7 +4506,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B4">
         <v>10.855000000000018</v>
@@ -4507,7 +4514,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B5">
         <v>61.525000000000006</v>
@@ -4515,7 +4522,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B6">
         <v>69.59</v>
@@ -4523,7 +4530,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="B7">
         <v>54.240000000000038</v>
@@ -4531,7 +4538,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B8">
         <v>61.525000000000006</v>
@@ -4539,7 +4546,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="B9">
         <v>79.33</v>
@@ -4547,7 +4554,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B10">
         <v>74.83</v>
@@ -4555,7 +4562,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="B11">
         <v>69.59</v>
@@ -4563,7 +4570,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="B12">
         <v>75.284999999999997</v>
@@ -4571,7 +4578,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B13">
         <v>84.28</v>
@@ -4579,7 +4586,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="B14">
         <v>90.37</v>
@@ -4587,7 +4594,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B15">
         <v>89.18</v>
@@ -4595,7 +4602,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B16">
         <v>61.525000000000006</v>
@@ -4603,7 +4610,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B17">
         <v>67.330000000000013</v>
@@ -4611,15 +4618,15 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="B18">
-        <v>69.59</v>
+        <v>63.715000000000003</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B19">
         <v>83.985000000000014</v>
@@ -4627,15 +4634,15 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B20">
-        <v>63.565000000000026</v>
+        <v>62.620000000000033</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B21">
         <v>4.4550000000000125</v>
@@ -4643,7 +4650,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="B22">
         <v>79.375000000000028</v>
@@ -4651,15 +4658,15 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="B23">
-        <v>67.330000000000013</v>
+        <v>65.445000000000022</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B24">
         <v>84.28</v>
@@ -4667,7 +4674,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="B25">
         <v>61.525000000000006</v>
@@ -4675,23 +4682,23 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B26">
-        <v>65.599999999999994</v>
+        <v>63.715000000000003</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="29" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="B27">
-        <v>65.599999999999994</v>
+        <v>63.715000000000003</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B28">
         <v>74.83</v>
@@ -4699,7 +4706,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="30" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B29">
         <v>73.22</v>
@@ -4707,7 +4714,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="B30">
         <v>69.83</v>
@@ -4715,7 +4722,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B31">
         <v>64.83</v>
@@ -4723,7 +4730,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B32">
         <v>58.33</v>
@@ -4731,7 +4738,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="B33">
         <v>52.600000000000023</v>
@@ -4739,15 +4746,15 @@
     </row>
     <row r="34" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="B34">
-        <v>65.599999999999994</v>
+        <v>63.715000000000003</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="6" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B35">
         <v>0</v>
